--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_mapping_params.xlsx
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46229.44717396117</v>
+        <v>46230.1708520238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
